--- a/research/traditional_assets/database/data/thailand/thailand_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0354</v>
+        <v>0.07575</v>
       </c>
       <c r="E2">
-        <v>0.0425</v>
+        <v>0.0283</v>
       </c>
       <c r="G2">
-        <v>0.1396374956827827</v>
+        <v>0.02128397863187255</v>
       </c>
       <c r="H2">
-        <v>0.1396374956827827</v>
+        <v>0.02128397863187255</v>
       </c>
       <c r="I2">
-        <v>0.03718053275313046</v>
+        <v>-0.3816198172661344</v>
       </c>
       <c r="J2">
-        <v>0.03354484685300246</v>
+        <v>-0.3263018727895992</v>
       </c>
       <c r="K2">
-        <v>71.271</v>
+        <v>-835.125</v>
       </c>
       <c r="L2">
-        <v>0.03371971442494665</v>
+        <v>-0.3948021557225925</v>
       </c>
       <c r="M2">
-        <v>117.421</v>
+        <v>114.9763</v>
       </c>
       <c r="N2">
-        <v>0.0343195767814345</v>
+        <v>0.04285028007498481</v>
       </c>
       <c r="O2">
-        <v>1.647528447755749</v>
+        <v>-0.1376755575512648</v>
       </c>
       <c r="P2">
-        <v>117.421</v>
+        <v>114.9763</v>
       </c>
       <c r="Q2">
-        <v>0.0343195767814345</v>
+        <v>0.04285028007498481</v>
       </c>
       <c r="R2">
-        <v>1.647528447755749</v>
+        <v>-0.1376755575512648</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>340.69</v>
+        <v>286.99</v>
       </c>
       <c r="V2">
-        <v>0.0995761968784708</v>
+        <v>0.1069577110997648</v>
       </c>
       <c r="W2">
-        <v>0.0597248341138354</v>
+        <v>0.03578403252513157</v>
       </c>
       <c r="X2">
-        <v>0.0614735306500052</v>
+        <v>0.09982327349628292</v>
       </c>
       <c r="Y2">
-        <v>-0.001748696536169804</v>
+        <v>-0.06403924097115135</v>
       </c>
       <c r="Z2">
-        <v>1.100587251992168</v>
+        <v>1.120667307205243</v>
       </c>
       <c r="AA2">
-        <v>0.07379535692150847</v>
+        <v>0.03647850490069849</v>
       </c>
       <c r="AB2">
-        <v>0.06086583613139504</v>
+        <v>0.09914076682572012</v>
       </c>
       <c r="AC2">
-        <v>0.01284139744606671</v>
+        <v>-0.06260104771628937</v>
       </c>
       <c r="AD2">
-        <v>38.967</v>
+        <v>54.92</v>
       </c>
       <c r="AE2">
-        <v>5.590552785004292</v>
+        <v>7.656997315270571</v>
       </c>
       <c r="AF2">
-        <v>44.55755278500429</v>
+        <v>62.57699731527057</v>
       </c>
       <c r="AG2">
-        <v>-296.1324472149957</v>
+        <v>-224.4130026847294</v>
       </c>
       <c r="AH2">
-        <v>0.01285576990093284</v>
+        <v>0.02279018633872768</v>
       </c>
       <c r="AI2">
-        <v>0.01981896927195309</v>
+        <v>0.06345476728143352</v>
       </c>
       <c r="AJ2">
-        <v>-0.0947542705427267</v>
+        <v>-0.09126943091673007</v>
       </c>
       <c r="AK2">
-        <v>-0.1552433118722315</v>
+        <v>-0.3209673709896635</v>
       </c>
       <c r="AL2">
-        <v>1.597</v>
+        <v>1.691</v>
       </c>
       <c r="AM2">
-        <v>1.597</v>
+        <v>1.691</v>
       </c>
       <c r="AN2">
-        <v>0.4188828929546578</v>
+        <v>-0.0691308047470155</v>
       </c>
       <c r="AO2">
-        <v>47.14464621164684</v>
+        <v>-480.2176227084565</v>
       </c>
       <c r="AP2">
-        <v>-3.183329899329173</v>
+        <v>0.2824809080715494</v>
       </c>
       <c r="AQ2">
-        <v>47.14464621164684</v>
+        <v>-480.2176227084565</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thaivivat Insurance Public Company Limited (SET:TVI)</t>
+          <t>Indara Insurance Public Company Limited (SET:INSURE)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,118 +722,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.157</v>
+        <v>0.356</v>
+      </c>
+      <c r="E3">
+        <v>1.654</v>
       </c>
       <c r="G3">
-        <v>0.02413388138578978</v>
+        <v>0.005370051635111876</v>
       </c>
       <c r="H3">
-        <v>0.02413388138578978</v>
+        <v>0.005370051635111876</v>
       </c>
       <c r="I3">
-        <v>0.1104408677992938</v>
+        <v>0.3514455149915428</v>
       </c>
       <c r="J3">
-        <v>0.08829394909698864</v>
+        <v>0.3444166046917119</v>
       </c>
       <c r="K3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L3">
-        <v>0.08807985907222547</v>
+        <v>0.3442340791738382</v>
       </c>
       <c r="M3">
-        <v>1.8</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.007269789983844911</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.12</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>1.8</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.007269789983844911</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.12</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>19.2</v>
+        <v>25.2</v>
       </c>
       <c r="V3">
-        <v>0.07754442649434572</v>
+        <v>0.3835616438356164</v>
       </c>
       <c r="W3">
-        <v>0.3571428571428572</v>
+        <v>4.37636761487965</v>
       </c>
       <c r="X3">
-        <v>0.06077895725155182</v>
+        <v>0.09923154359062185</v>
       </c>
       <c r="Y3">
-        <v>0.2963638998913053</v>
+        <v>4.277136071289028</v>
       </c>
       <c r="Z3">
-        <v>7.098613307390524</v>
+        <v>24.17732696968794</v>
       </c>
       <c r="AA3">
-        <v>0.6267646020219452</v>
+        <v>8.327072865421279</v>
       </c>
       <c r="AB3">
-        <v>0.06076821734281005</v>
+        <v>0.09951941365395986</v>
       </c>
       <c r="AC3">
-        <v>0.5659963846791352</v>
+        <v>8.227553451767319</v>
       </c>
       <c r="AD3">
-        <v>0.08699999999999999</v>
+        <v>0.451</v>
       </c>
       <c r="AE3">
-        <v>0.009601068901288524</v>
+        <v>0.02507789495680106</v>
       </c>
       <c r="AF3">
-        <v>0.09660106890128851</v>
+        <v>0.4760778949568011</v>
       </c>
       <c r="AG3">
-        <v>-19.10339893109871</v>
+        <v>-24.7239221050432</v>
       </c>
       <c r="AH3">
-        <v>0.0003899975554142432</v>
+        <v>0.007194108658305397</v>
       </c>
       <c r="AI3">
-        <v>0.001894264850529376</v>
+        <v>0.01861418693327784</v>
       </c>
       <c r="AJ3">
-        <v>-0.0836047400343528</v>
+        <v>-0.6033745388815296</v>
       </c>
       <c r="AK3">
-        <v>-0.600800031729895</v>
+        <v>-65.74149248490914</v>
       </c>
       <c r="AL3">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="AM3">
-        <v>0.003</v>
+        <v>0.013</v>
       </c>
       <c r="AN3">
-        <v>0.004436511983681794</v>
+        <v>0.02208186447316882</v>
       </c>
       <c r="AO3">
-        <v>6266.666666666667</v>
+        <v>1569.230769230769</v>
       </c>
       <c r="AP3">
-        <v>-0.9741661872054415</v>
+        <v>-1.2105328096868</v>
       </c>
       <c r="AQ3">
-        <v>6266.666666666667</v>
+        <v>1569.230769230769</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dhipaya Group Holdings Public Company Limited (SET:TIPH)</t>
+          <t>Thaivivat Insurance Public Company Limited (SET:TVI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,46 +853,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0699</v>
+        <v>0.166</v>
       </c>
       <c r="E4">
-        <v>0.0425</v>
+        <v>0.329</v>
       </c>
       <c r="G4">
-        <v>0.223279098873592</v>
+        <v>0.1154562383612663</v>
       </c>
       <c r="H4">
-        <v>0.223279098873592</v>
+        <v>0.1154562383612663</v>
       </c>
       <c r="I4">
-        <v>0.1956522319174374</v>
+        <v>0.04710519156856033</v>
       </c>
       <c r="J4">
-        <v>0.1583120673946324</v>
+        <v>0.0375085280399455</v>
       </c>
       <c r="K4">
-        <v>61.8</v>
+        <v>6.01</v>
       </c>
       <c r="L4">
-        <v>0.1546933667083855</v>
+        <v>0.03730602110490379</v>
       </c>
       <c r="M4">
-        <v>32.1</v>
+        <v>5.62</v>
       </c>
       <c r="N4">
-        <v>0.02339479629764595</v>
+        <v>0.05342205323193917</v>
       </c>
       <c r="O4">
-        <v>0.5194174757281553</v>
+        <v>0.9351081530782031</v>
       </c>
       <c r="P4">
-        <v>32.1</v>
+        <v>5.62</v>
       </c>
       <c r="Q4">
-        <v>0.02339479629764595</v>
+        <v>0.05342205323193917</v>
       </c>
       <c r="R4">
-        <v>0.5194174757281553</v>
+        <v>0.9351081530782031</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,67 +901,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>93.09999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="V4">
-        <v>0.06785219736170833</v>
+        <v>0.08479087452471483</v>
       </c>
       <c r="W4">
-        <v>0.2576073363901625</v>
+        <v>0.119009900990099</v>
       </c>
       <c r="X4">
-        <v>0.0608335203950107</v>
+        <v>0.09894893023478574</v>
       </c>
       <c r="Y4">
-        <v>0.1967738159951518</v>
+        <v>0.02006097075531327</v>
       </c>
       <c r="Z4">
-        <v>2.16443571073655</v>
+        <v>5.199664503963493</v>
       </c>
       <c r="AA4">
-        <v>0.3426562921094737</v>
+        <v>0.195031761845224</v>
       </c>
       <c r="AB4">
-        <v>0.06077469451031393</v>
+        <v>0.09889944062856212</v>
       </c>
       <c r="AC4">
-        <v>0.2818815975991598</v>
+        <v>0.0961323212166619</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.077</v>
       </c>
       <c r="AE4">
-        <v>2.584666744918749</v>
+        <v>0.06676819152465947</v>
       </c>
       <c r="AF4">
-        <v>2.584666744918749</v>
+        <v>0.1437681915246595</v>
       </c>
       <c r="AG4">
-        <v>-90.51533325508125</v>
+        <v>-8.776231808475341</v>
       </c>
       <c r="AH4">
-        <v>0.001880188822531146</v>
+        <v>0.001364752694846416</v>
       </c>
       <c r="AI4">
-        <v>0.009251283454573322</v>
+        <v>0.003017565507134559</v>
       </c>
       <c r="AJ4">
-        <v>-0.07062766557981694</v>
+        <v>-0.09101730800484049</v>
       </c>
       <c r="AK4">
-        <v>-0.4858979262046548</v>
+        <v>-0.2266368232830235</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.009286058851905451</v>
+      </c>
+      <c r="AO4">
+        <v>3765</v>
       </c>
       <c r="AP4">
-        <v>-1.092125159930999</v>
+        <v>-1.058397468460605</v>
+      </c>
+      <c r="AQ4">
+        <v>3765</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bangkok Union Insurance Public Company Limited (SET:BUI)</t>
+          <t>Nam Seng Insurance Public Company Limited (SET:NSI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,46 +987,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0407</v>
+        <v>0.0599</v>
       </c>
       <c r="E5">
-        <v>0.337</v>
+        <v>-0.018</v>
       </c>
       <c r="G5">
-        <v>0.04075342465753425</v>
+        <v>0.070098730606488</v>
       </c>
       <c r="H5">
-        <v>0.04075342465753425</v>
+        <v>0.070098730606488</v>
       </c>
       <c r="I5">
-        <v>0.1356164383561644</v>
+        <v>0.05450048537515385</v>
       </c>
       <c r="J5">
-        <v>0.1101369863013699</v>
+        <v>0.04422580370606747</v>
       </c>
       <c r="K5">
-        <v>3.21</v>
+        <v>2.97</v>
       </c>
       <c r="L5">
-        <v>0.1099315068493151</v>
+        <v>0.04188998589562765</v>
       </c>
       <c r="M5">
-        <v>0.223</v>
+        <v>2.58</v>
       </c>
       <c r="N5">
-        <v>0.01</v>
+        <v>0.03115942028985507</v>
       </c>
       <c r="O5">
-        <v>0.06947040498442368</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="P5">
-        <v>0.223</v>
+        <v>2.58</v>
       </c>
       <c r="Q5">
-        <v>0.01</v>
+        <v>0.03115942028985507</v>
       </c>
       <c r="R5">
-        <v>0.06947040498442368</v>
+        <v>0.8686868686868686</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1029,67 +1035,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>9.210000000000001</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="V5">
-        <v>0.4130044843049328</v>
+        <v>0.1182367149758454</v>
       </c>
       <c r="W5">
-        <v>0.1465753424657534</v>
+        <v>0.07333333333333333</v>
       </c>
       <c r="X5">
-        <v>0.06341858138532609</v>
+        <v>0.09904496007898836</v>
       </c>
       <c r="Y5">
-        <v>0.08315676108042734</v>
+        <v>-0.02571162674565503</v>
       </c>
       <c r="Z5">
-        <v>1.541710665258712</v>
+        <v>4.22235481838161</v>
       </c>
       <c r="AA5">
-        <v>0.1697993664202746</v>
+        <v>0.1867370353751132</v>
       </c>
       <c r="AB5">
-        <v>0.06137475198092733</v>
+        <v>0.09892304251850888</v>
       </c>
       <c r="AC5">
-        <v>0.1084246144393472</v>
+        <v>0.08781399285660436</v>
       </c>
       <c r="AD5">
-        <v>1.62</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>0.2095779345079589</v>
       </c>
       <c r="AF5">
-        <v>1.62</v>
+        <v>0.278577934507959</v>
       </c>
       <c r="AG5">
-        <v>-7.590000000000001</v>
+        <v>-9.51142206549204</v>
       </c>
       <c r="AH5">
-        <v>0.0677257525083612</v>
+        <v>0.003353186121307541</v>
       </c>
       <c r="AI5">
-        <v>0.06347962382445142</v>
+        <v>0.008524787555513117</v>
       </c>
       <c r="AJ5">
-        <v>-0.5159755268524814</v>
+        <v>-0.1297804150872135</v>
       </c>
       <c r="AK5">
-        <v>-0.4653586756591049</v>
+        <v>-0.4155532114187028</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AN5">
-        <v>0.3616071428571428</v>
+        <v>0.01672321861366941</v>
+      </c>
+      <c r="AO5">
+        <v>1226.666666666667</v>
       </c>
       <c r="AP5">
-        <v>-1.694196428571429</v>
+        <v>-2.305240442436267</v>
+      </c>
+      <c r="AQ5">
+        <v>1226.666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Muang Thai Insurance Public Company Limited (SET:MTI)</t>
+          <t>Dhipaya Group Holdings Public Company Limited (SET:TIPH)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,46 +1121,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0301</v>
+        <v>0.0901</v>
       </c>
       <c r="E6">
-        <v>-0.00459</v>
+        <v>-0.0917</v>
       </c>
       <c r="G6">
-        <v>0.09106015287470921</v>
+        <v>0.1846273695144118</v>
       </c>
       <c r="H6">
-        <v>0.09106015287470921</v>
+        <v>0.1846273695144118</v>
       </c>
       <c r="I6">
-        <v>0.09233238879777808</v>
+        <v>0.09179744803613078</v>
       </c>
       <c r="J6">
-        <v>0.07372758536212093</v>
+        <v>0.07539476923343656</v>
       </c>
       <c r="K6">
-        <v>21.3</v>
+        <v>25.8</v>
       </c>
       <c r="L6">
-        <v>0.07078763708873381</v>
+        <v>0.06699558556219164</v>
       </c>
       <c r="M6">
-        <v>7.91</v>
+        <v>28.3</v>
       </c>
       <c r="N6">
-        <v>0.04046035805626599</v>
+        <v>0.03578654527061204</v>
       </c>
       <c r="O6">
-        <v>0.3713615023474178</v>
+        <v>1.096899224806202</v>
       </c>
       <c r="P6">
-        <v>7.91</v>
+        <v>28.3</v>
       </c>
       <c r="Q6">
-        <v>0.04046035805626599</v>
+        <v>0.03578654527061204</v>
       </c>
       <c r="R6">
-        <v>0.3713615023474178</v>
+        <v>1.096899224806202</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1157,73 +1169,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>3.46</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="V6">
-        <v>0.01769820971867008</v>
+        <v>0.08232169954476479</v>
       </c>
       <c r="W6">
-        <v>0.1351522842639594</v>
+        <v>0.09409190371991248</v>
       </c>
       <c r="X6">
-        <v>0.06149084019489329</v>
+        <v>0.1004632158889479</v>
       </c>
       <c r="Y6">
-        <v>0.07366144406906611</v>
+        <v>-0.006371312169035442</v>
       </c>
       <c r="Z6">
-        <v>2.211103085977343</v>
+        <v>2.063838984671271</v>
       </c>
       <c r="AA6">
-        <v>0.1630192915158436</v>
+        <v>0.1556026639842605</v>
       </c>
       <c r="AB6">
-        <v>0.06086825879065714</v>
+        <v>0.09926098466004525</v>
       </c>
       <c r="AC6">
-        <v>0.1021510327251864</v>
+        <v>0.05634167932421526</v>
       </c>
       <c r="AD6">
-        <v>2.1</v>
+        <v>20.5</v>
       </c>
       <c r="AE6">
-        <v>1.785921053742892</v>
+        <v>5.49401380643018</v>
       </c>
       <c r="AF6">
-        <v>3.885921053742892</v>
+        <v>25.99401380643018</v>
       </c>
       <c r="AG6">
-        <v>0.4259210537428917</v>
+        <v>-39.10598619356981</v>
       </c>
       <c r="AH6">
-        <v>0.01948944555967657</v>
+        <v>0.03182444210786103</v>
       </c>
       <c r="AI6">
-        <v>0.02210598568104241</v>
+        <v>0.1013830760731211</v>
       </c>
       <c r="AJ6">
-        <v>0.002173888230062528</v>
+        <v>-0.05202380952263384</v>
       </c>
       <c r="AK6">
-        <v>0.00247160178305422</v>
+        <v>-0.2044286980832606</v>
       </c>
       <c r="AL6">
-        <v>0.07199999999999999</v>
+        <v>0.113</v>
       </c>
       <c r="AM6">
-        <v>0.07199999999999999</v>
+        <v>0.113</v>
       </c>
       <c r="AN6">
-        <v>0.0696748506967485</v>
+        <v>0.5183312262958281</v>
       </c>
       <c r="AO6">
-        <v>372.2222222222223</v>
+        <v>283.1858407079646</v>
       </c>
       <c r="AP6">
-        <v>0.01413142182292275</v>
+        <v>-0.9887733550839395</v>
       </c>
       <c r="AQ6">
-        <v>372.2222222222223</v>
+        <v>283.1858407079646</v>
       </c>
     </row>
     <row r="7">
@@ -1234,7 +1246,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nam Seng Insurance Public Company Limited (SET:NSI)</t>
+          <t>Muang Thai Insurance Public Company Limited (SET:MTI)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1243,46 +1255,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0457</v>
+        <v>0.0392</v>
       </c>
       <c r="E7">
-        <v>0.0593</v>
+        <v>0.0746</v>
       </c>
       <c r="G7">
-        <v>0.09900142653352355</v>
+        <v>0.1075231879079354</v>
       </c>
       <c r="H7">
-        <v>0.09900142653352355</v>
+        <v>0.1075231879079354</v>
       </c>
       <c r="I7">
-        <v>0.06285493590004522</v>
+        <v>0.09919608566621553</v>
       </c>
       <c r="J7">
-        <v>0.05213966587518037</v>
+        <v>0.07946391466858345</v>
       </c>
       <c r="K7">
-        <v>3.48</v>
+        <v>22.3</v>
       </c>
       <c r="L7">
-        <v>0.04964336661911555</v>
+        <v>0.07660597732737891</v>
       </c>
       <c r="M7">
-        <v>3.2</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="N7">
-        <v>0.09439528023598821</v>
+        <v>0.0385673624288425</v>
       </c>
       <c r="O7">
-        <v>0.9195402298850576</v>
+        <v>0.3645739910313902</v>
       </c>
       <c r="P7">
-        <v>3.2</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="Q7">
-        <v>0.09439528023598821</v>
+        <v>0.0385673624288425</v>
       </c>
       <c r="R7">
-        <v>0.9195402298850576</v>
+        <v>0.3645739910313902</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1291,73 +1303,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="V7">
-        <v>0.7079646017699115</v>
+        <v>0.06641366223908918</v>
       </c>
       <c r="W7">
-        <v>0.07963386727688787</v>
+        <v>0.1297265852239674</v>
       </c>
       <c r="X7">
-        <v>0.06110560821530409</v>
+        <v>0.09951031846591255</v>
       </c>
       <c r="Y7">
-        <v>0.01852825906158378</v>
+        <v>0.03021626675805489</v>
       </c>
       <c r="Z7">
-        <v>2.897610797775998</v>
+        <v>1.902488823367371</v>
       </c>
       <c r="AA7">
-        <v>0.1510804588323554</v>
+        <v>0.1511792095179985</v>
       </c>
       <c r="AB7">
-        <v>0.06081382869391551</v>
+        <v>0.09903609810943668</v>
       </c>
       <c r="AC7">
-        <v>0.09026663013843987</v>
+        <v>0.0521431114085618</v>
       </c>
       <c r="AD7">
-        <v>0.082</v>
+        <v>1.48</v>
       </c>
       <c r="AE7">
-        <v>0.2343449670341537</v>
+        <v>1.270097312823277</v>
       </c>
       <c r="AF7">
-        <v>0.3163449670341537</v>
+        <v>2.750097312823277</v>
       </c>
       <c r="AG7">
-        <v>-23.68365503296585</v>
+        <v>-11.24990268717672</v>
       </c>
       <c r="AH7">
-        <v>0.009245434231474382</v>
+        <v>0.01287799606475824</v>
       </c>
       <c r="AI7">
-        <v>0.007750448191518712</v>
+        <v>0.0173452893402977</v>
       </c>
       <c r="AJ7">
-        <v>-2.318212150175789</v>
+        <v>-0.05637633275387931</v>
       </c>
       <c r="AK7">
-        <v>-1.408371146012644</v>
+        <v>-0.07782701565970322</v>
       </c>
       <c r="AL7">
-        <v>0.002</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AM7">
-        <v>0.002</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="AN7">
-        <v>0.01739868448970932</v>
+        <v>0.04831864185439112</v>
       </c>
       <c r="AO7">
-        <v>2105</v>
+        <v>392.9577464788733</v>
       </c>
       <c r="AP7">
-        <v>-5.025176115630351</v>
+        <v>-0.3672837965124624</v>
       </c>
       <c r="AQ7">
-        <v>2105</v>
+        <v>392.9577464788733</v>
       </c>
     </row>
     <row r="8">
@@ -1377,46 +1389,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.143</v>
+        <v>0.229</v>
       </c>
       <c r="E8">
-        <v>0.176</v>
+        <v>0.152</v>
       </c>
       <c r="G8">
-        <v>0.1074230537115269</v>
+        <v>0.2102621305075293</v>
       </c>
       <c r="H8">
-        <v>0.1074230537115269</v>
+        <v>0.2102621305075293</v>
       </c>
       <c r="I8">
-        <v>0.2094146047073024</v>
+        <v>0.1293920803123257</v>
       </c>
       <c r="J8">
-        <v>0.2094146047073024</v>
+        <v>0.1225035810726767</v>
       </c>
       <c r="K8">
-        <v>39.6</v>
+        <v>26.4</v>
       </c>
       <c r="L8">
-        <v>0.2389861194930598</v>
+        <v>0.147239263803681</v>
       </c>
       <c r="M8">
-        <v>17</v>
+        <v>15.9613</v>
       </c>
       <c r="N8">
-        <v>0.0364103662454487</v>
+        <v>0.03395298872580303</v>
       </c>
       <c r="O8">
-        <v>0.4292929292929293</v>
+        <v>0.604594696969697</v>
       </c>
       <c r="P8">
-        <v>17</v>
+        <v>15.9613</v>
       </c>
       <c r="Q8">
-        <v>0.0364103662454487</v>
+        <v>0.03395298872580303</v>
       </c>
       <c r="R8">
-        <v>0.4292929292929293</v>
+        <v>0.604594696969697</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1425,73 +1437,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>46.4</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="V8">
-        <v>0.09937888198757765</v>
+        <v>0.1384811742182514</v>
       </c>
       <c r="W8">
-        <v>0.07283428361228618</v>
+        <v>0.05348460291734197</v>
       </c>
       <c r="X8">
-        <v>0.06122086241827156</v>
+        <v>0.09943742352495759</v>
       </c>
       <c r="Y8">
-        <v>0.01161342119401462</v>
+        <v>-0.04595282060761562</v>
       </c>
       <c r="Z8">
-        <v>0.4302443330823358</v>
+        <v>0.4094261639988126</v>
       </c>
       <c r="AA8">
-        <v>0.09009944693999429</v>
+        <v>0.05015617127470357</v>
       </c>
       <c r="AB8">
-        <v>0.06083023202242465</v>
+        <v>0.09891366969197216</v>
       </c>
       <c r="AC8">
-        <v>0.02926921491756964</v>
+        <v>-0.04875749841726858</v>
       </c>
       <c r="AD8">
-        <v>5.83</v>
+        <v>5.42</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>5.83</v>
+        <v>5.42</v>
       </c>
       <c r="AG8">
-        <v>-40.57</v>
+        <v>-59.67999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.01233262115795486</v>
+        <v>0.01139804845222073</v>
       </c>
       <c r="AI8">
-        <v>0.01167330757063052</v>
+        <v>0.020132233860783</v>
       </c>
       <c r="AJ8">
-        <v>-0.09516102549668098</v>
+        <v>-0.1454120169582379</v>
       </c>
       <c r="AK8">
-        <v>-0.08955256826258746</v>
+        <v>-0.2923770331177738</v>
       </c>
       <c r="AL8">
-        <v>0.195</v>
+        <v>0.185</v>
       </c>
       <c r="AM8">
-        <v>0.195</v>
+        <v>0.185</v>
       </c>
       <c r="AN8">
-        <v>0.1665714285714286</v>
+        <v>0.2286919831223629</v>
       </c>
       <c r="AO8">
-        <v>177.948717948718</v>
+        <v>125.4054054054054</v>
       </c>
       <c r="AP8">
-        <v>-1.159142857142857</v>
+        <v>-2.518143459915612</v>
       </c>
       <c r="AQ8">
-        <v>177.948717948718</v>
+        <v>125.4054054054054</v>
       </c>
     </row>
     <row r="9">
@@ -1511,43 +1523,46 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0105</v>
+        <v>0.0311</v>
+      </c>
+      <c r="E9">
+        <v>-0.227</v>
       </c>
       <c r="G9">
-        <v>0.04418052256532067</v>
+        <v>0.05968790637191157</v>
       </c>
       <c r="H9">
-        <v>0.04418052256532067</v>
+        <v>0.05968790637191157</v>
       </c>
       <c r="I9">
-        <v>0.04677067456766022</v>
+        <v>0.02826046528322066</v>
       </c>
       <c r="J9">
-        <v>0.0398339003621196</v>
+        <v>0.01705877826681454</v>
       </c>
       <c r="K9">
-        <v>3.03</v>
+        <v>1.17</v>
       </c>
       <c r="L9">
-        <v>0.03598574821852731</v>
+        <v>0.01521456436931079</v>
       </c>
       <c r="M9">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="N9">
-        <v>0.0325</v>
+        <v>0.04112426035502958</v>
       </c>
       <c r="O9">
-        <v>0.5148514851485149</v>
+        <v>1.188034188034188</v>
       </c>
       <c r="P9">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="Q9">
-        <v>0.0325</v>
+        <v>0.04112426035502958</v>
       </c>
       <c r="R9">
-        <v>0.5148514851485149</v>
+        <v>1.188034188034188</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1556,73 +1571,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>8.5</v>
+        <v>12.3</v>
       </c>
       <c r="V9">
-        <v>0.1770833333333333</v>
+        <v>0.363905325443787</v>
       </c>
       <c r="W9">
-        <v>0.04661538461538461</v>
+        <v>0.01808346213292117</v>
       </c>
       <c r="X9">
-        <v>0.06179181471912516</v>
+        <v>0.1003961320480086</v>
       </c>
       <c r="Y9">
-        <v>-0.01517643010374054</v>
+        <v>-0.08231266991508739</v>
       </c>
       <c r="Z9">
-        <v>1.443274858358949</v>
+        <v>1.336604425596482</v>
       </c>
       <c r="AA9">
-        <v>0.05749126690302266</v>
+        <v>0.0228008385266934</v>
       </c>
       <c r="AB9">
-        <v>0.06107768692845887</v>
+        <v>0.09924543554200355</v>
       </c>
       <c r="AC9">
-        <v>-0.003586420025436216</v>
+        <v>-0.07644459701531015</v>
       </c>
       <c r="AD9">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="AE9">
-        <v>0.02954600701504351</v>
+        <v>0.01385109860165414</v>
       </c>
       <c r="AF9">
-        <v>1.349546007015044</v>
+        <v>1.063851098601654</v>
       </c>
       <c r="AG9">
-        <v>-7.150453992984956</v>
+        <v>-11.23614890139835</v>
       </c>
       <c r="AH9">
-        <v>0.02734667522216325</v>
+        <v>0.03051444591112094</v>
       </c>
       <c r="AI9">
-        <v>0.02043232828385693</v>
+        <v>0.01848123567652508</v>
       </c>
       <c r="AJ9">
-        <v>-0.1750436587901618</v>
+        <v>-0.4979712395857231</v>
       </c>
       <c r="AK9">
-        <v>-0.1242486603128606</v>
+        <v>-0.2482366972470327</v>
       </c>
       <c r="AL9">
-        <v>0.074</v>
+        <v>0.053</v>
       </c>
       <c r="AM9">
-        <v>0.074</v>
+        <v>0.053</v>
       </c>
       <c r="AN9">
-        <v>0.3017832647462277</v>
+        <v>0.4124116260801257</v>
       </c>
       <c r="AO9">
-        <v>53.10810810810811</v>
+        <v>40.9433962264151</v>
       </c>
       <c r="AP9">
-        <v>-1.634763144258106</v>
+        <v>-4.413255656480105</v>
       </c>
       <c r="AQ9">
-        <v>53.10810810810811</v>
+        <v>40.9433962264151</v>
       </c>
     </row>
     <row r="10">
@@ -1633,7 +1648,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bangkok Insurance Public Company Limited (SET:BKI)</t>
+          <t>Bangkok Union Insurance Public Company Limited (SET:BUI)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1642,46 +1657,43 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.06509999999999999</v>
-      </c>
-      <c r="E10">
-        <v>-0.144</v>
+        <v>0.0614</v>
       </c>
       <c r="G10">
-        <v>0.2084098420859346</v>
+        <v>0.1613114754098361</v>
       </c>
       <c r="H10">
-        <v>0.2084098420859346</v>
+        <v>0.1613114754098361</v>
       </c>
       <c r="I10">
-        <v>0.0710613294160852</v>
+        <v>0.02154098360655738</v>
       </c>
       <c r="J10">
-        <v>0.06581226588321704</v>
+        <v>0.01077049180327869</v>
       </c>
       <c r="K10">
-        <v>34.7</v>
+        <v>-0.103</v>
       </c>
       <c r="L10">
-        <v>0.06371648916636063</v>
+        <v>-0.003377049180327869</v>
       </c>
       <c r="M10">
-        <v>39.6</v>
+        <v>0.795</v>
       </c>
       <c r="N10">
-        <v>0.04628330995792426</v>
+        <v>0.05096153846153847</v>
       </c>
       <c r="O10">
-        <v>1.141210374639769</v>
+        <v>-7.718446601941748</v>
       </c>
       <c r="P10">
-        <v>39.6</v>
+        <v>0.795</v>
       </c>
       <c r="Q10">
-        <v>0.04628330995792426</v>
+        <v>0.05096153846153847</v>
       </c>
       <c r="R10">
-        <v>1.141210374639769</v>
+        <v>-7.718446601941748</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1690,73 +1702,67 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>19.5</v>
+        <v>10.4</v>
       </c>
       <c r="V10">
-        <v>0.02279102384291725</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="W10">
-        <v>0.04026923523267959</v>
+        <v>-0.004309623430962343</v>
       </c>
       <c r="X10">
-        <v>0.06183213553977299</v>
+        <v>0.103227722117859</v>
       </c>
       <c r="Y10">
-        <v>-0.0215629003070934</v>
+        <v>-0.1075373455488213</v>
       </c>
       <c r="Z10">
-        <v>0.6195394976337822</v>
+        <v>1.870018393623544</v>
       </c>
       <c r="AA10">
-        <v>0.04077329814342919</v>
+        <v>0.02014101778050276</v>
       </c>
       <c r="AB10">
-        <v>0.06091554920845581</v>
+        <v>0.09986714058605967</v>
       </c>
       <c r="AC10">
-        <v>-0.02014225106502662</v>
+        <v>-0.07972612280555691</v>
       </c>
       <c r="AD10">
-        <v>25</v>
+        <v>1.41</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>25</v>
+        <v>1.41</v>
       </c>
       <c r="AG10">
-        <v>5.5</v>
+        <v>-8.99</v>
       </c>
       <c r="AH10">
-        <v>0.02838973427208721</v>
+        <v>0.08289241622574957</v>
       </c>
       <c r="AI10">
-        <v>0.02535496957403651</v>
+        <v>0.06555090655509065</v>
       </c>
       <c r="AJ10">
-        <v>0.006387179189408895</v>
+        <v>-1.360060514372164</v>
       </c>
       <c r="AK10">
-        <v>0.005690636316606311</v>
+        <v>-0.8091809180918091</v>
       </c>
       <c r="AL10">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN10">
-        <v>0.5924170616113744</v>
-      </c>
-      <c r="AO10">
-        <v>32.52100840336135</v>
+        <v>1.194915254237288</v>
       </c>
       <c r="AP10">
-        <v>0.1303317535545024</v>
-      </c>
-      <c r="AQ10">
-        <v>32.52100840336135</v>
+        <v>-7.618644067796611</v>
       </c>
     </row>
     <row r="11">
@@ -1776,103 +1782,100 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.0527</v>
+        <v>0.158</v>
       </c>
       <c r="E11">
-        <v>-0.204</v>
+        <v>-0.153</v>
       </c>
       <c r="G11">
-        <v>0.4044265593561368</v>
+        <v>-0.105607476635514</v>
       </c>
       <c r="H11">
-        <v>0.4044265593561368</v>
+        <v>-0.105607476635514</v>
       </c>
       <c r="I11">
-        <v>0.03553728079505592</v>
+        <v>0.02019292339623134</v>
       </c>
       <c r="J11">
-        <v>0.03553728079505592</v>
+        <v>0.02019292339623134</v>
       </c>
       <c r="K11">
-        <v>0.25</v>
+        <v>0.185</v>
       </c>
       <c r="L11">
-        <v>0.05030181086519115</v>
+        <v>0.01728971962616823</v>
       </c>
       <c r="M11">
-        <v>0.928</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.08672897196261684</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>3.712</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>0.928</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.08672897196261684</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>3.712</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="V11">
-        <v>0.1523364485981308</v>
+        <v>0.1845056065239551</v>
       </c>
       <c r="W11">
-        <v>0.01506024096385542</v>
+        <v>0.01201298701298701</v>
       </c>
       <c r="X11">
-        <v>0.06095896656138034</v>
+        <v>0.09912665451707992</v>
       </c>
       <c r="Y11">
-        <v>-0.04589872559752492</v>
+        <v>-0.0871136675040929</v>
       </c>
       <c r="Z11">
-        <v>0.3298621794107003</v>
+        <v>0.7742582379097428</v>
       </c>
       <c r="AA11">
-        <v>0.01172240489338717</v>
+        <v>0.0156345372870125</v>
       </c>
       <c r="AB11">
-        <v>0.06079280937908217</v>
+        <v>0.09889669246817226</v>
       </c>
       <c r="AC11">
-        <v>-0.049070404485695</v>
+        <v>-0.08326215518115976</v>
       </c>
       <c r="AD11">
         <v>0</v>
       </c>
       <c r="AE11">
-        <v>0.05689857224286036</v>
+        <v>0.04967859830162313</v>
       </c>
       <c r="AF11">
-        <v>0.05689857224286036</v>
+        <v>0.04967859830162313</v>
       </c>
       <c r="AG11">
-        <v>-1.57310142775714</v>
+        <v>-1.760321401698377</v>
       </c>
       <c r="AH11">
-        <v>0.00528949602533965</v>
+        <v>0.005038561633254506</v>
       </c>
       <c r="AI11">
-        <v>0.003681111833459106</v>
+        <v>0.00351093475067243</v>
       </c>
       <c r="AJ11">
-        <v>-0.1723588155719542</v>
+        <v>-0.2186821970842142</v>
       </c>
       <c r="AK11">
-        <v>-0.1137710976570769</v>
+        <v>-0.1426553688311347</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -1884,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>-7.865507138785699</v>
+        <v>-7.522741032899048</v>
       </c>
     </row>
     <row r="12">
@@ -1895,7 +1898,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indara Insurance Public Company Limited (SET:INSURE)</t>
+          <t>The Thai Setakij Insurance Public Company Limited (SET:TSI)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1904,25 +1907,25 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0524</v>
+        <v>-0.0256</v>
       </c>
       <c r="G12">
-        <v>-0.07029914529914531</v>
+        <v>-0.09571428571428572</v>
       </c>
       <c r="H12">
-        <v>-0.07029914529914531</v>
+        <v>-0.09571428571428572</v>
       </c>
       <c r="I12">
-        <v>-0.002942153001115424</v>
+        <v>-0.0008719507880191894</v>
       </c>
       <c r="J12">
-        <v>-0.002942153001115424</v>
+        <v>-0.0008719507880191894</v>
       </c>
       <c r="K12">
-        <v>0.081</v>
+        <v>-0.657</v>
       </c>
       <c r="L12">
-        <v>0.008653846153846154</v>
+        <v>-0.04692857142857143</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1931,7 +1934,7 @@
         <v>-0</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P12">
         <v>-0</v>
@@ -1940,79 +1943,79 @@
         <v>-0</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2.41</v>
+        <v>4.57</v>
       </c>
       <c r="V12">
-        <v>0.2190909090909091</v>
+        <v>0.3195804195804196</v>
       </c>
       <c r="W12">
-        <v>0.01597633136094674</v>
+        <v>-0.0619811320754717</v>
       </c>
       <c r="X12">
-        <v>0.06163048314678545</v>
+        <v>0.1019892058567579</v>
       </c>
       <c r="Y12">
-        <v>-0.0456541517858387</v>
+        <v>-0.1639703379322296</v>
       </c>
       <c r="Z12">
-        <v>3.205816764963421</v>
+        <v>2.473045327226472</v>
       </c>
       <c r="AA12">
-        <v>-0.00943200341606327</v>
+        <v>-0.002156373821882296</v>
       </c>
       <c r="AB12">
-        <v>0.0609732368876626</v>
+        <v>0.0994191614719977</v>
       </c>
       <c r="AC12">
-        <v>-0.07040524030372587</v>
+        <v>-0.10157553529388</v>
       </c>
       <c r="AD12">
-        <v>0.218</v>
+        <v>0.703</v>
       </c>
       <c r="AE12">
-        <v>0.0426927604522018</v>
+        <v>0.2210365551613432</v>
       </c>
       <c r="AF12">
-        <v>0.2606927604522018</v>
+        <v>0.9240365551613432</v>
       </c>
       <c r="AG12">
-        <v>-2.149307239547798</v>
+        <v>-3.645963444838657</v>
       </c>
       <c r="AH12">
-        <v>0.02315068584126196</v>
+        <v>0.06069589703185985</v>
       </c>
       <c r="AI12">
-        <v>0.05396591614901178</v>
+        <v>0.09046732407614209</v>
       </c>
       <c r="AJ12">
-        <v>-0.2428405660121441</v>
+        <v>-0.3422142796264737</v>
       </c>
       <c r="AK12">
-        <v>-0.8878893160924285</v>
+        <v>-0.6459850869506695</v>
       </c>
       <c r="AL12">
-        <v>0.008999999999999999</v>
+        <v>0.095</v>
       </c>
       <c r="AM12">
-        <v>0.008999999999999999</v>
+        <v>0.095</v>
       </c>
       <c r="AN12">
-        <v>218.0000000000006</v>
+        <v>3.623711340206185</v>
       </c>
       <c r="AO12">
-        <v>-5.444444444444445</v>
+        <v>-0.6105263157894737</v>
       </c>
       <c r="AP12">
-        <v>-2149.307239547804</v>
+        <v>-18.79362600432297</v>
       </c>
       <c r="AQ12">
-        <v>-5.444444444444445</v>
+        <v>-0.6105263157894737</v>
       </c>
     </row>
     <row r="13">
@@ -2023,7 +2026,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Thai Setakij Insurance Public Company Limited (SET:TSI)</t>
+          <t>Bangkok Insurance Public Company Limited (SET:BKI)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2032,115 +2035,118 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.0428</v>
+        <v>0.108</v>
       </c>
       <c r="G13">
-        <v>-0.1645833333333333</v>
+        <v>0.06490021801106827</v>
       </c>
       <c r="H13">
-        <v>-0.1645833333333333</v>
+        <v>0.06490021801106827</v>
       </c>
       <c r="I13">
-        <v>-0.1432536287553318</v>
+        <v>-0.08385041086701325</v>
       </c>
       <c r="J13">
-        <v>-0.1432536287553318</v>
+        <v>-0.08385041086701325</v>
       </c>
       <c r="K13">
-        <v>-2.38</v>
+        <v>-51.4</v>
       </c>
       <c r="L13">
-        <v>-0.1652777777777778</v>
+        <v>-0.08619822237128963</v>
       </c>
       <c r="M13">
-        <v>-0</v>
+        <v>52.2</v>
       </c>
       <c r="N13">
-        <v>-0</v>
+        <v>0.06074711974863262</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>-1.015564202334631</v>
       </c>
       <c r="P13">
-        <v>-0</v>
+        <v>52.2</v>
       </c>
       <c r="Q13">
-        <v>-0</v>
+        <v>0.06074711974863262</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>-1.015564202334631</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
       <c r="U13">
-        <v>5.58</v>
+        <v>20</v>
       </c>
       <c r="V13">
-        <v>0.2644549763033175</v>
+        <v>0.02327475852438031</v>
       </c>
       <c r="W13">
-        <v>-0.163013698630137</v>
+        <v>-0.05348595213319459</v>
       </c>
       <c r="X13">
-        <v>0.06244284768903238</v>
+        <v>0.1001362285266533</v>
       </c>
       <c r="Y13">
-        <v>-0.2254565463191694</v>
+        <v>-0.1536221806598479</v>
       </c>
       <c r="Z13">
-        <v>1.532035293600459</v>
+        <v>0.6169684428349715</v>
       </c>
       <c r="AA13">
-        <v>-0.2194696151895058</v>
+        <v>-0.05173305742369374</v>
       </c>
       <c r="AB13">
-        <v>0.06116031045617065</v>
+        <v>0.09895106375873021</v>
       </c>
       <c r="AC13">
-        <v>-0.2806299256456765</v>
+        <v>-0.1506841211824239</v>
       </c>
       <c r="AD13">
-        <v>0.42</v>
+        <v>22.4</v>
       </c>
       <c r="AE13">
-        <v>0.5492612703838871</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.969261270383887</v>
+        <v>22.4</v>
       </c>
       <c r="AG13">
-        <v>-4.610738729616113</v>
+        <v>2.399999999999999</v>
       </c>
       <c r="AH13">
-        <v>0.04391906274110765</v>
+        <v>0.02540546671203357</v>
       </c>
       <c r="AI13">
-        <v>0.08377901127231828</v>
+        <v>0.0249832701316083</v>
       </c>
       <c r="AJ13">
-        <v>-0.2796206970106896</v>
+        <v>0.002785192062202621</v>
       </c>
       <c r="AK13">
-        <v>-0.7698342953271403</v>
+        <v>0.0027378507871321</v>
       </c>
       <c r="AL13">
-        <v>0.006</v>
+        <v>1.12</v>
       </c>
       <c r="AM13">
-        <v>0.006</v>
+        <v>1.12</v>
       </c>
       <c r="AN13">
-        <v>-0.2368866328257191</v>
+        <v>-0.4806866952789699</v>
       </c>
       <c r="AO13">
-        <v>-381.6666666666667</v>
+        <v>-44.64285714285714</v>
       </c>
       <c r="AP13">
-        <v>2.600529458328321</v>
+        <v>-0.05150214592274675</v>
       </c>
       <c r="AQ13">
-        <v>-381.6666666666667</v>
+        <v>-44.64285714285714</v>
       </c>
     </row>
     <row r="14">
@@ -2160,118 +2166,106 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0107</v>
+        <v>-0.00228</v>
       </c>
       <c r="G14">
-        <v>0.1008114856429463</v>
+        <v>-0.682552838789888</v>
       </c>
       <c r="H14">
-        <v>0.1008114856429463</v>
+        <v>-0.682552838789888</v>
       </c>
       <c r="I14">
-        <v>-0.4056133709989471</v>
+        <v>-3.645144546973032</v>
       </c>
       <c r="J14">
-        <v>-0.4056133709989471</v>
+        <v>-3.645144546973032</v>
       </c>
       <c r="K14">
-        <v>-108.8</v>
+        <v>-887.8</v>
       </c>
       <c r="L14">
-        <v>-0.3395755305867665</v>
+        <v>-3.679237463738085</v>
       </c>
       <c r="M14">
-        <v>13.1</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.0958302852962692</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>-0.1204044117647059</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>13.1</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.0958302852962692</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>-0.1204044117647059</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>107.7</v>
+        <v>49.8</v>
       </c>
       <c r="V14">
-        <v>0.7878566203365034</v>
+        <v>1.992</v>
       </c>
       <c r="W14">
-        <v>-0.5144208037825059</v>
+        <v>-9.88641425389755</v>
       </c>
       <c r="X14">
-        <v>0.06145622110511712</v>
+        <v>0.1020881219066696</v>
       </c>
       <c r="Y14">
-        <v>-0.575877024887623</v>
-      </c>
-      <c r="Z14">
-        <v>1.75294983818833</v>
-      </c>
-      <c r="AA14">
-        <v>-0.7110198930596272</v>
+        <v>-9.98850237580422</v>
       </c>
       <c r="AB14">
-        <v>0.06086341347213295</v>
-      </c>
-      <c r="AC14">
-        <v>-0.7718833065317602</v>
+        <v>0.09962518662751838</v>
       </c>
       <c r="AD14">
-        <v>2.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE14">
-        <v>0.2976203403132174</v>
+        <v>0.3068959229630742</v>
       </c>
       <c r="AF14">
-        <v>2.587620340313217</v>
+        <v>1.666895922963074</v>
       </c>
       <c r="AG14">
-        <v>-105.1123796596868</v>
+        <v>-48.13310407703693</v>
       </c>
       <c r="AH14">
-        <v>0.01857753283451205</v>
+        <v>0.06250805972238024</v>
       </c>
       <c r="AI14">
-        <v>0.02800830166186359</v>
+        <v>-0.002073426152635884</v>
       </c>
       <c r="AJ14">
-        <v>-3.327644771187108</v>
+        <v>2.080702352643468</v>
       </c>
       <c r="AK14">
-        <v>6.864535885066793</v>
+        <v>0.0563795685644323</v>
       </c>
       <c r="AL14">
-        <v>0.046</v>
+        <v>0.036</v>
       </c>
       <c r="AM14">
-        <v>0.046</v>
+        <v>0.036</v>
       </c>
       <c r="AN14">
-        <v>-0.01777964114628219</v>
+        <v>-0.001547719844499677</v>
       </c>
       <c r="AO14">
-        <v>-2828.260869565217</v>
+        <v>-24436.11111111111</v>
       </c>
       <c r="AP14">
-        <v>0.816096240341049</v>
+        <v>0.05477688261573408</v>
       </c>
       <c r="AQ14">
-        <v>-2828.260869565217</v>
+        <v>-24436.11111111111</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/thailand/thailand_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ14"/>
+  <dimension ref="A1:AQ12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07575</v>
+        <v>0.09934999999999999</v>
       </c>
       <c r="E2">
-        <v>0.0283</v>
+        <v>0.09275</v>
       </c>
       <c r="G2">
-        <v>0.02128397863187255</v>
+        <v>0.06480940594059406</v>
       </c>
       <c r="H2">
-        <v>0.02128397863187255</v>
+        <v>0.06480940594059406</v>
       </c>
       <c r="I2">
-        <v>-0.3816198172661344</v>
+        <v>0.1247208669588904</v>
       </c>
       <c r="J2">
-        <v>-0.3263018727895992</v>
+        <v>0.1072697844828328</v>
       </c>
       <c r="K2">
-        <v>-835.125</v>
+        <v>210.47</v>
       </c>
       <c r="L2">
-        <v>-0.3948021557225925</v>
+        <v>0.1041930693069307</v>
       </c>
       <c r="M2">
-        <v>114.9763</v>
+        <v>98.321</v>
       </c>
       <c r="N2">
-        <v>0.04285028007498481</v>
+        <v>0.04459588789455302</v>
       </c>
       <c r="O2">
-        <v>-0.1376755575512648</v>
+        <v>0.4671497125481066</v>
       </c>
       <c r="P2">
-        <v>114.9763</v>
+        <v>98.321</v>
       </c>
       <c r="Q2">
-        <v>0.04285028007498481</v>
+        <v>0.04459588789455302</v>
       </c>
       <c r="R2">
-        <v>-0.1376755575512648</v>
+        <v>0.4671497125481066</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>286.99</v>
+        <v>192.343</v>
       </c>
       <c r="V2">
-        <v>0.1069577110997648</v>
+        <v>0.08724185947358157</v>
       </c>
       <c r="W2">
-        <v>0.03578403252513157</v>
+        <v>0.1221391259487331</v>
       </c>
       <c r="X2">
-        <v>0.09982327349628292</v>
+        <v>0.0854973612759522</v>
       </c>
       <c r="Y2">
-        <v>-0.06403924097115135</v>
+        <v>0.03664176467278088</v>
       </c>
       <c r="Z2">
-        <v>1.120667307205243</v>
+        <v>1.387339536906161</v>
       </c>
       <c r="AA2">
-        <v>0.03647850490069849</v>
+        <v>0.1563205379511341</v>
       </c>
       <c r="AB2">
-        <v>0.09914076682572012</v>
+        <v>0.08483344050459815</v>
       </c>
       <c r="AC2">
-        <v>-0.06260104771628937</v>
+        <v>0.07167907327797127</v>
       </c>
       <c r="AD2">
-        <v>54.92</v>
+        <v>61.885</v>
       </c>
       <c r="AE2">
-        <v>7.656997315270571</v>
+        <v>6.494243715207428</v>
       </c>
       <c r="AF2">
-        <v>62.57699731527057</v>
+        <v>68.37924371520742</v>
       </c>
       <c r="AG2">
-        <v>-224.4130026847294</v>
+        <v>-123.9637562847926</v>
       </c>
       <c r="AH2">
-        <v>0.02279018633872768</v>
+        <v>0.03008207614560978</v>
       </c>
       <c r="AI2">
-        <v>0.06345476728143352</v>
+        <v>0.03451807438815437</v>
       </c>
       <c r="AJ2">
-        <v>-0.09126943091673007</v>
+        <v>-0.05957658540017509</v>
       </c>
       <c r="AK2">
-        <v>-0.3209673709896635</v>
+        <v>-0.06930668535160475</v>
       </c>
       <c r="AL2">
-        <v>1.691</v>
+        <v>2.14</v>
       </c>
       <c r="AM2">
-        <v>1.691</v>
+        <v>2.14</v>
       </c>
       <c r="AN2">
-        <v>-0.0691308047470155</v>
+        <v>0.2355325505718472</v>
       </c>
       <c r="AO2">
-        <v>-480.2176227084565</v>
+        <v>115.5686915887851</v>
       </c>
       <c r="AP2">
-        <v>0.2824809080715494</v>
+        <v>-0.4718025320550062</v>
       </c>
       <c r="AQ2">
-        <v>-480.2176227084565</v>
+        <v>115.5686915887851</v>
       </c>
     </row>
     <row r="3">
@@ -722,28 +722,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.356</v>
-      </c>
-      <c r="E3">
-        <v>1.654</v>
+        <v>0.403</v>
       </c>
       <c r="G3">
-        <v>0.005370051635111876</v>
+        <v>0.2458432304038005</v>
       </c>
       <c r="H3">
-        <v>0.005370051635111876</v>
+        <v>0.2458432304038005</v>
       </c>
       <c r="I3">
-        <v>0.3514455149915428</v>
+        <v>0.041852980733636</v>
       </c>
       <c r="J3">
-        <v>0.3444166046917119</v>
+        <v>0.03510133942904086</v>
       </c>
       <c r="K3">
-        <v>20</v>
+        <v>2.93</v>
       </c>
       <c r="L3">
-        <v>0.3442340791738382</v>
+        <v>0.03479809976247031</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -767,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>25.2</v>
+        <v>19.7</v>
       </c>
       <c r="V3">
-        <v>0.3835616438356164</v>
+        <v>0.5487465181058496</v>
       </c>
       <c r="W3">
-        <v>4.37636761487965</v>
+        <v>0.1167330677290837</v>
       </c>
       <c r="X3">
-        <v>0.09923154359062185</v>
+        <v>0.08492742464145747</v>
       </c>
       <c r="Y3">
-        <v>4.277136071289028</v>
+        <v>0.03180564308762619</v>
       </c>
       <c r="Z3">
-        <v>24.17732696968794</v>
+        <v>230.1205931334706</v>
       </c>
       <c r="AA3">
-        <v>8.327072865421279</v>
+        <v>8.077541049190161</v>
       </c>
       <c r="AB3">
-        <v>0.09951941365395986</v>
+        <v>0.0851673467754073</v>
       </c>
       <c r="AC3">
-        <v>8.227553451767319</v>
+        <v>7.992373702414754</v>
       </c>
       <c r="AD3">
-        <v>0.451</v>
+        <v>0.294</v>
       </c>
       <c r="AE3">
-        <v>0.02507789495680106</v>
+        <v>0.01489511113924141</v>
       </c>
       <c r="AF3">
-        <v>0.4760778949568011</v>
+        <v>0.3088951111392414</v>
       </c>
       <c r="AG3">
-        <v>-24.7239221050432</v>
+        <v>-19.39110488886076</v>
       </c>
       <c r="AH3">
-        <v>0.007194108658305397</v>
+        <v>0.008530917891615352</v>
       </c>
       <c r="AI3">
-        <v>0.01861418693327784</v>
+        <v>0.01050345856149628</v>
       </c>
       <c r="AJ3">
-        <v>-0.6033745388815296</v>
+        <v>-1.174585261964429</v>
       </c>
       <c r="AK3">
-        <v>-65.74149248490914</v>
+        <v>-1.997251455174636</v>
       </c>
       <c r="AL3">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="AM3">
-        <v>0.013</v>
+        <v>0.017</v>
       </c>
       <c r="AN3">
-        <v>0.02208186447316882</v>
+        <v>0.08312128922815945</v>
       </c>
       <c r="AO3">
-        <v>1569.230769230769</v>
+        <v>206.4705882352941</v>
       </c>
       <c r="AP3">
-        <v>-1.2105328096868</v>
+        <v>-5.482359312655007</v>
       </c>
       <c r="AQ3">
-        <v>1569.230769230769</v>
+        <v>206.4705882352941</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thaivivat Insurance Public Company Limited (SET:TVI)</t>
+          <t>Bangkok Union Insurance Public Company Limited (SET:BUI)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,46 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.166</v>
+        <v>0.0358</v>
       </c>
       <c r="E4">
-        <v>0.329</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="G4">
-        <v>0.1154562383612663</v>
+        <v>0.0859016393442623</v>
       </c>
       <c r="H4">
-        <v>0.1154562383612663</v>
+        <v>0.0859016393442623</v>
       </c>
       <c r="I4">
-        <v>0.04710519156856033</v>
+        <v>0.1829508196721311</v>
       </c>
       <c r="J4">
-        <v>0.0375085280399455</v>
+        <v>0.1495081967213115</v>
       </c>
       <c r="K4">
-        <v>6.01</v>
+        <v>4.56</v>
       </c>
       <c r="L4">
-        <v>0.03730602110490379</v>
+        <v>0.1495081967213115</v>
       </c>
       <c r="M4">
-        <v>5.62</v>
+        <v>0.41</v>
       </c>
       <c r="N4">
-        <v>0.05342205323193917</v>
+        <v>0.02192513368983957</v>
       </c>
       <c r="O4">
-        <v>0.9351081530782031</v>
+        <v>0.08991228070175439</v>
       </c>
       <c r="P4">
-        <v>5.62</v>
+        <v>0.41</v>
       </c>
       <c r="Q4">
-        <v>0.05342205323193917</v>
+        <v>0.02192513368983957</v>
       </c>
       <c r="R4">
-        <v>0.9351081530782031</v>
+        <v>0.08991228070175439</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,73 +898,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>8.92</v>
+        <v>7.3</v>
       </c>
       <c r="V4">
-        <v>0.08479087452471483</v>
+        <v>0.3903743315508021</v>
       </c>
       <c r="W4">
-        <v>0.119009900990099</v>
+        <v>0.226865671641791</v>
       </c>
       <c r="X4">
-        <v>0.09894893023478574</v>
+        <v>0.08737550300051611</v>
       </c>
       <c r="Y4">
-        <v>0.02006097075531327</v>
+        <v>0.1394901686412749</v>
       </c>
       <c r="Z4">
-        <v>5.199664503963493</v>
+        <v>2.745274527452745</v>
       </c>
       <c r="AA4">
-        <v>0.195031761845224</v>
+        <v>0.4104410441044103</v>
       </c>
       <c r="AB4">
-        <v>0.09889944062856212</v>
+        <v>0.0852282474054025</v>
       </c>
       <c r="AC4">
-        <v>0.0961323212166619</v>
+        <v>0.3252127966990078</v>
       </c>
       <c r="AD4">
-        <v>0.077</v>
+        <v>1.41</v>
       </c>
       <c r="AE4">
-        <v>0.06676819152465947</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.1437681915246595</v>
+        <v>1.41</v>
       </c>
       <c r="AG4">
-        <v>-8.776231808475341</v>
+        <v>-5.89</v>
       </c>
       <c r="AH4">
-        <v>0.001364752694846416</v>
+        <v>0.07011437095972153</v>
       </c>
       <c r="AI4">
-        <v>0.003017565507134559</v>
+        <v>0.05505661850839515</v>
       </c>
       <c r="AJ4">
-        <v>-0.09101730800484049</v>
+        <v>-0.4597970335675254</v>
       </c>
       <c r="AK4">
-        <v>-0.2266368232830235</v>
+        <v>-0.3216821409066084</v>
       </c>
       <c r="AL4">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.009286058851905451</v>
-      </c>
-      <c r="AO4">
-        <v>3765</v>
+        <v>0.2486772486772487</v>
       </c>
       <c r="AP4">
-        <v>-1.058397468460605</v>
-      </c>
-      <c r="AQ4">
-        <v>3765</v>
+        <v>-1.038800705467372</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nam Seng Insurance Public Company Limited (SET:NSI)</t>
+          <t>Dhipaya Group Holdings Public Company Limited (SET:TIPH)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,46 +978,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0599</v>
+        <v>0.102</v>
       </c>
       <c r="E5">
-        <v>-0.018</v>
+        <v>0.0204</v>
       </c>
       <c r="G5">
-        <v>0.070098730606488</v>
+        <v>0.1087058823529412</v>
       </c>
       <c r="H5">
-        <v>0.070098730606488</v>
+        <v>0.1087058823529412</v>
       </c>
       <c r="I5">
-        <v>0.05450048537515385</v>
+        <v>0.1422938985521089</v>
       </c>
       <c r="J5">
-        <v>0.04422580370606747</v>
+        <v>0.1145415424515203</v>
       </c>
       <c r="K5">
-        <v>2.97</v>
+        <v>44.7</v>
       </c>
       <c r="L5">
-        <v>0.04188998589562765</v>
+        <v>0.1051764705882353</v>
       </c>
       <c r="M5">
-        <v>2.58</v>
+        <v>20.7</v>
       </c>
       <c r="N5">
-        <v>0.03115942028985507</v>
+        <v>0.04105513685045617</v>
       </c>
       <c r="O5">
-        <v>0.8686868686868686</v>
+        <v>0.4630872483221476</v>
       </c>
       <c r="P5">
-        <v>2.58</v>
+        <v>20.7</v>
       </c>
       <c r="Q5">
-        <v>0.03115942028985507</v>
+        <v>0.04105513685045617</v>
       </c>
       <c r="R5">
-        <v>0.8686868686868686</v>
+        <v>0.4630872483221476</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1035,73 +1026,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>9.789999999999999</v>
+        <v>49.2</v>
       </c>
       <c r="V5">
-        <v>0.1182367149758454</v>
+        <v>0.0975803252677509</v>
       </c>
       <c r="W5">
-        <v>0.07333333333333333</v>
+        <v>0.1966564012318522</v>
       </c>
       <c r="X5">
-        <v>0.09904496007898836</v>
+        <v>0.08695087327909243</v>
       </c>
       <c r="Y5">
-        <v>-0.02571162674565503</v>
+        <v>0.1097055279527598</v>
       </c>
       <c r="Z5">
-        <v>4.22235481838161</v>
+        <v>2.289186578373382</v>
       </c>
       <c r="AA5">
-        <v>0.1867370353751132</v>
+        <v>0.2622069616462053</v>
       </c>
       <c r="AB5">
-        <v>0.09892304251850888</v>
+        <v>0.08501116226554301</v>
       </c>
       <c r="AC5">
-        <v>0.08781399285660436</v>
+        <v>0.1771957993806623</v>
       </c>
       <c r="AD5">
-        <v>0.06900000000000001</v>
+        <v>27.3</v>
       </c>
       <c r="AE5">
-        <v>0.2095779345079589</v>
+        <v>4.87546557676849</v>
       </c>
       <c r="AF5">
-        <v>0.278577934507959</v>
+        <v>32.17546557676849</v>
       </c>
       <c r="AG5">
-        <v>-9.51142206549204</v>
+        <v>-17.02453442323151</v>
       </c>
       <c r="AH5">
-        <v>0.003353186121307541</v>
+        <v>0.05998683318255427</v>
       </c>
       <c r="AI5">
-        <v>0.008524787555513117</v>
+        <v>0.1192233814511601</v>
       </c>
       <c r="AJ5">
-        <v>-0.1297804150872135</v>
+        <v>-0.03494538544357138</v>
       </c>
       <c r="AK5">
-        <v>-0.4155532114187028</v>
+        <v>-0.07714738192003055</v>
       </c>
       <c r="AL5">
-        <v>0.003</v>
+        <v>0.62</v>
       </c>
       <c r="AM5">
-        <v>0.003</v>
+        <v>0.62</v>
       </c>
       <c r="AN5">
-        <v>0.01672321861366941</v>
+        <v>0.4222737819025522</v>
       </c>
       <c r="AO5">
-        <v>1226.666666666667</v>
+        <v>91.93548387096774</v>
       </c>
       <c r="AP5">
-        <v>-2.305240442436267</v>
+        <v>-0.2633338657885771</v>
       </c>
       <c r="AQ5">
-        <v>1226.666666666667</v>
+        <v>91.93548387096774</v>
       </c>
     </row>
     <row r="6">
@@ -1112,7 +1103,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dhipaya Group Holdings Public Company Limited (SET:TIPH)</t>
+          <t>Allianz Ayudhya Capital Public Company Limited (SET:AYUD)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1121,46 +1112,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0901</v>
+        <v>0.286</v>
       </c>
       <c r="E6">
-        <v>-0.0917</v>
+        <v>0.0413</v>
       </c>
       <c r="G6">
-        <v>0.1846273695144118</v>
+        <v>0.1330724070450098</v>
       </c>
       <c r="H6">
-        <v>0.1846273695144118</v>
+        <v>0.1330724070450098</v>
       </c>
       <c r="I6">
-        <v>0.09179744803613078</v>
+        <v>0.1076320939334638</v>
       </c>
       <c r="J6">
-        <v>0.07539476923343656</v>
+        <v>0.1006708142263243</v>
       </c>
       <c r="K6">
-        <v>25.8</v>
+        <v>18.8</v>
       </c>
       <c r="L6">
-        <v>0.06699558556219164</v>
+        <v>0.07358121330724071</v>
       </c>
       <c r="M6">
-        <v>28.3</v>
+        <v>16.7</v>
       </c>
       <c r="N6">
-        <v>0.03578654527061204</v>
+        <v>0.04377457404980341</v>
       </c>
       <c r="O6">
-        <v>1.096899224806202</v>
+        <v>0.8882978723404255</v>
       </c>
       <c r="P6">
-        <v>28.3</v>
+        <v>16.7</v>
       </c>
       <c r="Q6">
-        <v>0.03578654527061204</v>
+        <v>0.04377457404980341</v>
       </c>
       <c r="R6">
-        <v>1.096899224806202</v>
+        <v>0.8882978723404255</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1169,73 +1160,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>65.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="V6">
-        <v>0.08232169954476479</v>
+        <v>0.1832241153342071</v>
       </c>
       <c r="W6">
-        <v>0.09409190371991248</v>
+        <v>0.0712661106899166</v>
       </c>
       <c r="X6">
-        <v>0.1004632158889479</v>
+        <v>0.08517023002281345</v>
       </c>
       <c r="Y6">
-        <v>-0.006371312169035442</v>
+        <v>-0.01390411933289684</v>
       </c>
       <c r="Z6">
-        <v>2.063838984671271</v>
+        <v>1.668625914315569</v>
       </c>
       <c r="AA6">
-        <v>0.1556026639842605</v>
+        <v>0.1679819294332933</v>
       </c>
       <c r="AB6">
-        <v>0.09926098466004525</v>
+        <v>0.08464212966571791</v>
       </c>
       <c r="AC6">
-        <v>0.05634167932421526</v>
+        <v>0.08333979976757536</v>
       </c>
       <c r="AD6">
-        <v>20.5</v>
+        <v>5.81</v>
       </c>
       <c r="AE6">
-        <v>5.49401380643018</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>25.99401380643018</v>
+        <v>5.81</v>
       </c>
       <c r="AG6">
-        <v>-39.10598619356981</v>
+        <v>-64.09</v>
       </c>
       <c r="AH6">
-        <v>0.03182444210786103</v>
+        <v>0.01500090366889572</v>
       </c>
       <c r="AI6">
-        <v>0.1013830760731211</v>
+        <v>0.01920597666192853</v>
       </c>
       <c r="AJ6">
-        <v>-0.05202380952263384</v>
+        <v>-0.2019155036073218</v>
       </c>
       <c r="AK6">
-        <v>-0.2044286980832606</v>
+        <v>-0.2755255578006105</v>
       </c>
       <c r="AL6">
-        <v>0.113</v>
+        <v>0.187</v>
       </c>
       <c r="AM6">
-        <v>0.113</v>
+        <v>0.187</v>
       </c>
       <c r="AN6">
-        <v>0.5183312262958281</v>
+        <v>0.2075</v>
       </c>
       <c r="AO6">
-        <v>283.1858407079646</v>
+        <v>147.0588235294118</v>
       </c>
       <c r="AP6">
-        <v>-0.9887733550839395</v>
+        <v>-2.288928571428571</v>
       </c>
       <c r="AQ6">
-        <v>283.1858407079646</v>
+        <v>147.0588235294118</v>
       </c>
     </row>
     <row r="7">
@@ -1246,7 +1237,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Muang Thai Insurance Public Company Limited (SET:MTI)</t>
+          <t>Thaivivat Holdings Public Company Limited (SET:TVH)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1255,46 +1246,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0392</v>
+        <v>0.172</v>
       </c>
       <c r="E7">
-        <v>0.0746</v>
+        <v>0.104</v>
       </c>
       <c r="G7">
-        <v>0.1075231879079354</v>
+        <v>0.04269311064718163</v>
       </c>
       <c r="H7">
-        <v>0.1075231879079354</v>
+        <v>0.04269311064718163</v>
       </c>
       <c r="I7">
-        <v>0.09919608566621553</v>
+        <v>0.04167252789045875</v>
       </c>
       <c r="J7">
-        <v>0.07946391466858345</v>
+        <v>0.0329076511175285</v>
       </c>
       <c r="K7">
-        <v>22.3</v>
+        <v>6.32</v>
       </c>
       <c r="L7">
-        <v>0.07660597732737891</v>
+        <v>0.03298538622129436</v>
       </c>
       <c r="M7">
-        <v>8.130000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="N7">
-        <v>0.0385673624288425</v>
+        <v>0.03337969401947148</v>
       </c>
       <c r="O7">
-        <v>0.3645739910313902</v>
+        <v>0.3797468354430379</v>
       </c>
       <c r="P7">
-        <v>8.130000000000001</v>
+        <v>2.4</v>
       </c>
       <c r="Q7">
-        <v>0.0385673624288425</v>
+        <v>0.03337969401947148</v>
       </c>
       <c r="R7">
-        <v>0.3645739910313902</v>
+        <v>0.3797468354430379</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1303,73 +1294,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>14</v>
+        <v>5.93</v>
       </c>
       <c r="V7">
-        <v>0.06641366223908918</v>
+        <v>0.08247566063977746</v>
       </c>
       <c r="W7">
-        <v>0.1297265852239674</v>
+        <v>0.1338983050847458</v>
       </c>
       <c r="X7">
-        <v>0.09951031846591255</v>
+        <v>0.08467514223720414</v>
       </c>
       <c r="Y7">
-        <v>0.03021626675805489</v>
+        <v>0.04922316284754162</v>
       </c>
       <c r="Z7">
-        <v>1.902488823367371</v>
+        <v>5.030360921750315</v>
       </c>
       <c r="AA7">
-        <v>0.1511792095179985</v>
+        <v>0.1655373622082085</v>
       </c>
       <c r="AB7">
-        <v>0.09903609810943668</v>
+        <v>0.08462350706769832</v>
       </c>
       <c r="AC7">
-        <v>0.0521431114085618</v>
+        <v>0.08091385514051018</v>
       </c>
       <c r="AD7">
-        <v>1.48</v>
+        <v>0.061</v>
       </c>
       <c r="AE7">
-        <v>1.270097312823277</v>
+        <v>0.06271828094051753</v>
       </c>
       <c r="AF7">
-        <v>2.750097312823277</v>
+        <v>0.1237182809405175</v>
       </c>
       <c r="AG7">
-        <v>-11.24990268717672</v>
+        <v>-5.806281719059482</v>
       </c>
       <c r="AH7">
-        <v>0.01287799606475824</v>
+        <v>0.00171774359743458</v>
       </c>
       <c r="AI7">
-        <v>0.0173452893402977</v>
+        <v>0.002448716863089406</v>
       </c>
       <c r="AJ7">
-        <v>-0.05637633275387931</v>
+        <v>-0.08784922183344378</v>
       </c>
       <c r="AK7">
-        <v>-0.07782701565970322</v>
+        <v>-0.1302040274479893</v>
       </c>
       <c r="AL7">
-        <v>0.07099999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="AM7">
-        <v>0.07099999999999999</v>
+        <v>0.002</v>
       </c>
       <c r="AN7">
-        <v>0.04831864185439112</v>
+        <v>0.007103761499941772</v>
       </c>
       <c r="AO7">
-        <v>392.9577464788733</v>
+        <v>3965</v>
       </c>
       <c r="AP7">
-        <v>-0.3672837965124624</v>
+        <v>-0.6761711562896801</v>
       </c>
       <c r="AQ7">
-        <v>392.9577464788733</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="8">
@@ -1380,7 +1371,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Allianz Ayudhya Capital Public Company Limited (SET:AYUD)</t>
+          <t>Charan Insurance Public Company Limited (SET:CHARAN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1389,46 +1380,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.229</v>
+        <v>0.136</v>
       </c>
       <c r="E8">
-        <v>0.152</v>
+        <v>0.5529999999999999</v>
       </c>
       <c r="G8">
-        <v>0.2102621305075293</v>
+        <v>0.241747572815534</v>
       </c>
       <c r="H8">
-        <v>0.2102621305075293</v>
+        <v>0.241747572815534</v>
       </c>
       <c r="I8">
-        <v>0.1293920803123257</v>
+        <v>0.213501100136029</v>
       </c>
       <c r="J8">
-        <v>0.1225035810726767</v>
+        <v>0.178376725597521</v>
       </c>
       <c r="K8">
-        <v>26.4</v>
+        <v>1.81</v>
       </c>
       <c r="L8">
-        <v>0.147239263803681</v>
+        <v>0.1757281553398058</v>
       </c>
       <c r="M8">
-        <v>15.9613</v>
+        <v>0.656</v>
       </c>
       <c r="N8">
-        <v>0.03395298872580303</v>
+        <v>0.07951515151515152</v>
       </c>
       <c r="O8">
-        <v>0.604594696969697</v>
+        <v>0.3624309392265194</v>
       </c>
       <c r="P8">
-        <v>15.9613</v>
+        <v>0.656</v>
       </c>
       <c r="Q8">
-        <v>0.03395298872580303</v>
+        <v>0.07951515151515152</v>
       </c>
       <c r="R8">
-        <v>0.604594696969697</v>
+        <v>0.3624309392265194</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1437,73 +1428,67 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>65.09999999999999</v>
+        <v>0.973</v>
       </c>
       <c r="V8">
-        <v>0.1384811742182514</v>
+        <v>0.1179393939393939</v>
       </c>
       <c r="W8">
-        <v>0.05348460291734197</v>
+        <v>0.1283687943262412</v>
       </c>
       <c r="X8">
-        <v>0.09943742352495759</v>
+        <v>0.08549919358573758</v>
       </c>
       <c r="Y8">
-        <v>-0.04595282060761562</v>
+        <v>0.04286960074050357</v>
       </c>
       <c r="Z8">
-        <v>0.4094261639988126</v>
+        <v>0.8246799754917357</v>
       </c>
       <c r="AA8">
-        <v>0.05015617127470357</v>
+        <v>0.1471037136940597</v>
       </c>
       <c r="AB8">
-        <v>0.09891366969197216</v>
+        <v>0.08465942227862731</v>
       </c>
       <c r="AC8">
-        <v>-0.04875749841726858</v>
+        <v>0.06244429141543235</v>
       </c>
       <c r="AD8">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>0.1996933429945039</v>
       </c>
       <c r="AF8">
-        <v>5.42</v>
+        <v>0.1996933429945039</v>
       </c>
       <c r="AG8">
-        <v>-59.67999999999999</v>
+        <v>-0.7733066570054961</v>
       </c>
       <c r="AH8">
-        <v>0.01139804845222073</v>
+        <v>0.02363320595061195</v>
       </c>
       <c r="AI8">
-        <v>0.020132233860783</v>
+        <v>0.01280110695792504</v>
       </c>
       <c r="AJ8">
-        <v>-0.1454120169582379</v>
+        <v>-0.1034289653901704</v>
       </c>
       <c r="AK8">
-        <v>-0.2923770331177738</v>
+        <v>-0.05286954740019031</v>
       </c>
       <c r="AL8">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>0.2286919831223629</v>
-      </c>
-      <c r="AO8">
-        <v>125.4054054054054</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>-2.518143459915612</v>
-      </c>
-      <c r="AQ8">
-        <v>125.4054054054054</v>
+        <v>-0.3438446674101805</v>
       </c>
     </row>
     <row r="9">
@@ -1514,7 +1499,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Navakij Insurance Public Company Limited (SET:NKI)</t>
+          <t>Muang Thai Insurance Public Company Limited (SET:MTI)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1523,46 +1508,46 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0311</v>
+        <v>0.0599</v>
       </c>
       <c r="E9">
-        <v>-0.227</v>
+        <v>0.0825</v>
       </c>
       <c r="G9">
-        <v>0.05968790637191157</v>
+        <v>0.09406830437387656</v>
       </c>
       <c r="H9">
-        <v>0.05968790637191157</v>
+        <v>0.09406830437387656</v>
       </c>
       <c r="I9">
-        <v>0.02826046528322066</v>
+        <v>0.07223718516561822</v>
       </c>
       <c r="J9">
-        <v>0.01705877826681454</v>
+        <v>0.05621937454193766</v>
       </c>
       <c r="K9">
-        <v>1.17</v>
+        <v>17.9</v>
       </c>
       <c r="L9">
-        <v>0.01521456436931079</v>
+        <v>0.0536249251048532</v>
       </c>
       <c r="M9">
-        <v>1.39</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="N9">
-        <v>0.04112426035502958</v>
+        <v>0.05112820512820513</v>
       </c>
       <c r="O9">
-        <v>1.188034188034188</v>
+        <v>0.5569832402234638</v>
       </c>
       <c r="P9">
-        <v>1.39</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="Q9">
-        <v>0.04112426035502958</v>
+        <v>0.05112820512820513</v>
       </c>
       <c r="R9">
-        <v>1.188034188034188</v>
+        <v>0.5569832402234638</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1571,73 +1556,73 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>12.3</v>
+        <v>14.4</v>
       </c>
       <c r="V9">
-        <v>0.363905325443787</v>
+        <v>0.07384615384615385</v>
       </c>
       <c r="W9">
-        <v>0.01808346213292117</v>
+        <v>0.1148908857509627</v>
       </c>
       <c r="X9">
-        <v>0.1003961320480086</v>
+        <v>0.08522218104990735</v>
       </c>
       <c r="Y9">
-        <v>-0.08231266991508739</v>
+        <v>0.0296687047010554</v>
       </c>
       <c r="Z9">
-        <v>1.336604425596482</v>
+        <v>2.612585817599065</v>
       </c>
       <c r="AA9">
-        <v>0.0228008385266934</v>
+        <v>0.1468779406025562</v>
       </c>
       <c r="AB9">
-        <v>0.09924543554200355</v>
+        <v>0.08475597709765505</v>
       </c>
       <c r="AC9">
-        <v>-0.07644459701531015</v>
+        <v>0.06212196350490119</v>
       </c>
       <c r="AD9">
-        <v>1.05</v>
+        <v>2.06</v>
       </c>
       <c r="AE9">
-        <v>0.01385109860165414</v>
+        <v>1.186137958583187</v>
       </c>
       <c r="AF9">
-        <v>1.063851098601654</v>
+        <v>3.246137958583187</v>
       </c>
       <c r="AG9">
-        <v>-11.23614890139835</v>
+        <v>-11.15386204141681</v>
       </c>
       <c r="AH9">
-        <v>0.03051444591112094</v>
+        <v>0.01637428094191352</v>
       </c>
       <c r="AI9">
-        <v>0.01848123567652508</v>
+        <v>0.0192710738157816</v>
       </c>
       <c r="AJ9">
-        <v>-0.4979712395857231</v>
+        <v>-0.06066954772761967</v>
       </c>
       <c r="AK9">
-        <v>-0.2482366972470327</v>
+        <v>-0.07240598296865863</v>
       </c>
       <c r="AL9">
-        <v>0.053</v>
+        <v>0.073</v>
       </c>
       <c r="AM9">
-        <v>0.053</v>
+        <v>0.073</v>
       </c>
       <c r="AN9">
-        <v>0.4124116260801257</v>
+        <v>0.077882797731569</v>
       </c>
       <c r="AO9">
-        <v>40.9433962264151</v>
+        <v>316.4383561643836</v>
       </c>
       <c r="AP9">
-        <v>-4.413255656480105</v>
+        <v>-0.4216961074259665</v>
       </c>
       <c r="AQ9">
-        <v>40.9433962264151</v>
+        <v>316.4383561643836</v>
       </c>
     </row>
     <row r="10">
@@ -1648,7 +1633,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bangkok Union Insurance Public Company Limited (SET:BUI)</t>
+          <t>Bangkok Insurance Public Company Limited (SET:BKI)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1657,43 +1642,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0614</v>
+        <v>0.09669999999999999</v>
+      </c>
+      <c r="E10">
+        <v>0.103</v>
       </c>
       <c r="G10">
-        <v>0.1613114754098361</v>
+        <v>-0.02939166097060834</v>
       </c>
       <c r="H10">
-        <v>0.1613114754098361</v>
+        <v>-0.02939166097060834</v>
       </c>
       <c r="I10">
-        <v>0.02154098360655738</v>
+        <v>0.1997607655502392</v>
       </c>
       <c r="J10">
-        <v>0.01077049180327869</v>
+        <v>0.1925265597796644</v>
       </c>
       <c r="K10">
-        <v>-0.103</v>
+        <v>111.5</v>
       </c>
       <c r="L10">
-        <v>-0.003377049180327869</v>
+        <v>0.1905331510594668</v>
       </c>
       <c r="M10">
-        <v>0.795</v>
+        <v>46.5</v>
       </c>
       <c r="N10">
-        <v>0.05096153846153847</v>
+        <v>0.04894736842105263</v>
       </c>
       <c r="O10">
-        <v>-7.718446601941748</v>
+        <v>0.4170403587443946</v>
       </c>
       <c r="P10">
-        <v>0.795</v>
+        <v>46.5</v>
       </c>
       <c r="Q10">
-        <v>0.05096153846153847</v>
+        <v>0.04894736842105263</v>
       </c>
       <c r="R10">
-        <v>-7.718446601941748</v>
+        <v>0.4170403587443946</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1702,67 +1690,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>10.4</v>
+        <v>18.1</v>
       </c>
       <c r="V10">
-        <v>0.6666666666666667</v>
+        <v>0.01905263157894737</v>
       </c>
       <c r="W10">
-        <v>-0.004309623430962343</v>
+        <v>0.1275451841683825</v>
       </c>
       <c r="X10">
-        <v>0.103227722117859</v>
+        <v>0.0854955289661668</v>
       </c>
       <c r="Y10">
-        <v>-0.1075373455488213</v>
+        <v>0.04204965520221571</v>
       </c>
       <c r="Z10">
-        <v>1.870018393623544</v>
+        <v>0.6675792835957107</v>
       </c>
       <c r="AA10">
-        <v>0.02014101778050276</v>
+        <v>0.1285267428508552</v>
       </c>
       <c r="AB10">
-        <v>0.09986714058605967</v>
+        <v>0.08465923131032393</v>
       </c>
       <c r="AC10">
-        <v>-0.07972612280555691</v>
+        <v>0.04386751154053123</v>
       </c>
       <c r="AD10">
-        <v>1.41</v>
+        <v>22.9</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1.41</v>
+        <v>22.9</v>
       </c>
       <c r="AG10">
-        <v>-8.99</v>
+        <v>4.799999999999997</v>
       </c>
       <c r="AH10">
-        <v>0.08289241622574957</v>
+        <v>0.023537876451845</v>
       </c>
       <c r="AI10">
-        <v>0.06555090655509065</v>
+        <v>0.02184906020417899</v>
       </c>
       <c r="AJ10">
-        <v>-1.360060514372164</v>
+        <v>0.005027230833682444</v>
       </c>
       <c r="AK10">
-        <v>-0.8091809180918091</v>
+        <v>0.004660194174757278</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN10">
-        <v>1.194915254237288</v>
+        <v>0.1917922948073702</v>
+      </c>
+      <c r="AO10">
+        <v>103.4513274336283</v>
       </c>
       <c r="AP10">
-        <v>-7.618644067796611</v>
+        <v>0.0402010050251256</v>
+      </c>
+      <c r="AQ10">
+        <v>103.4513274336283</v>
       </c>
     </row>
     <row r="11">
@@ -1773,7 +1767,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Charan Insurance Public Company Limited (SET:CHARAN)</t>
+          <t>The Navakij Insurance Public Company Limited (SET:NKI)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1782,112 +1776,121 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.158</v>
+        <v>0.0599</v>
       </c>
       <c r="E11">
-        <v>-0.153</v>
+        <v>0.0549</v>
       </c>
       <c r="G11">
-        <v>-0.105607476635514</v>
+        <v>0.0208</v>
       </c>
       <c r="H11">
-        <v>-0.105607476635514</v>
+        <v>0.0208</v>
       </c>
       <c r="I11">
-        <v>0.02019292339623134</v>
+        <v>0.04861948641675887</v>
       </c>
       <c r="J11">
-        <v>0.02019292339623134</v>
+        <v>0.04071452991935173</v>
       </c>
       <c r="K11">
-        <v>0.185</v>
+        <v>3.56</v>
       </c>
       <c r="L11">
-        <v>0.01728971962616823</v>
+        <v>0.04068571428571428</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>0.985</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.03305369127516778</v>
       </c>
       <c r="O11">
-        <v>-0</v>
+        <v>0.2766853932584269</v>
       </c>
       <c r="P11">
-        <v>-0</v>
+        <v>0.985</v>
       </c>
       <c r="Q11">
-        <v>-0</v>
+        <v>0.03305369127516778</v>
       </c>
       <c r="R11">
-        <v>-0</v>
+        <v>0.2766853932584269</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
       <c r="U11">
-        <v>1.81</v>
+        <v>4.98</v>
       </c>
       <c r="V11">
-        <v>0.1845056065239551</v>
+        <v>0.1671140939597316</v>
       </c>
       <c r="W11">
-        <v>0.01201298701298701</v>
+        <v>0.06300884955752213</v>
       </c>
       <c r="X11">
-        <v>0.09912665451707992</v>
+        <v>0.08590216540622128</v>
       </c>
       <c r="Y11">
-        <v>-0.0871136675040929</v>
+        <v>-0.02289331584869915</v>
       </c>
       <c r="Z11">
-        <v>0.7742582379097428</v>
+        <v>1.933318211341962</v>
       </c>
       <c r="AA11">
-        <v>0.0156345372870125</v>
+        <v>0.07871414215930986</v>
       </c>
       <c r="AB11">
-        <v>0.09889669246817226</v>
+        <v>0.08491090391154124</v>
       </c>
       <c r="AC11">
-        <v>-0.08326215518115976</v>
+        <v>-0.006196761752231383</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE11">
-        <v>0.04967859830162313</v>
+        <v>0.008974692667993209</v>
       </c>
       <c r="AF11">
-        <v>0.04967859830162313</v>
+        <v>1.048974692667993</v>
       </c>
       <c r="AG11">
-        <v>-1.760321401698377</v>
+        <v>-3.931025307332007</v>
       </c>
       <c r="AH11">
-        <v>0.005038561633254506</v>
+        <v>0.03400355127255842</v>
       </c>
       <c r="AI11">
-        <v>0.00351093475067243</v>
+        <v>0.01707066225131264</v>
       </c>
       <c r="AJ11">
-        <v>-0.2186821970842142</v>
+        <v>-0.151959068885949</v>
       </c>
       <c r="AK11">
-        <v>-0.1426553688311347</v>
+        <v>-0.06961389557233127</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="AO11">
+        <v>94.44444444444444</v>
       </c>
       <c r="AP11">
-        <v>-7.522741032899048</v>
+        <v>-0.8590527332456308</v>
+      </c>
+      <c r="AQ11">
+        <v>94.44444444444444</v>
       </c>
     </row>
     <row r="12">
@@ -1907,25 +1910,25 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.0256</v>
+        <v>-0.00422</v>
       </c>
       <c r="G12">
-        <v>-0.09571428571428572</v>
+        <v>0.04298780487804878</v>
       </c>
       <c r="H12">
-        <v>-0.09571428571428572</v>
+        <v>0.04298780487804878</v>
       </c>
       <c r="I12">
-        <v>-0.0008719507880191894</v>
+        <v>-0.03617510673309141</v>
       </c>
       <c r="J12">
-        <v>-0.0008719507880191894</v>
+        <v>-0.03617510673309141</v>
       </c>
       <c r="K12">
-        <v>-0.657</v>
+        <v>-1.61</v>
       </c>
       <c r="L12">
-        <v>-0.04692857142857143</v>
+        <v>-0.09817073170731709</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1949,323 +1952,73 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>4.57</v>
+        <v>1.86</v>
       </c>
       <c r="V12">
-        <v>0.3195804195804196</v>
+        <v>0.1966173361522199</v>
       </c>
       <c r="W12">
-        <v>-0.0619811320754717</v>
+        <v>-0.1733046286329387</v>
       </c>
       <c r="X12">
-        <v>0.1019892058567579</v>
+        <v>0.08909201142494808</v>
       </c>
       <c r="Y12">
-        <v>-0.1639703379322296</v>
+        <v>-0.2623966400578868</v>
       </c>
       <c r="Z12">
-        <v>2.473045327226472</v>
+        <v>2.944683711347635</v>
       </c>
       <c r="AA12">
-        <v>-0.002156373821882296</v>
+        <v>-0.1065242475531965</v>
       </c>
       <c r="AB12">
-        <v>0.0994191614719977</v>
+        <v>0.08556929366289062</v>
       </c>
       <c r="AC12">
-        <v>-0.10157553529388</v>
+        <v>-0.1920935412160871</v>
       </c>
       <c r="AD12">
-        <v>0.703</v>
+        <v>1.01</v>
       </c>
       <c r="AE12">
-        <v>0.2210365551613432</v>
+        <v>0.146358752113495</v>
       </c>
       <c r="AF12">
-        <v>0.9240365551613432</v>
+        <v>1.156358752113495</v>
       </c>
       <c r="AG12">
-        <v>-3.645963444838657</v>
+        <v>-0.7036412478865051</v>
       </c>
       <c r="AH12">
-        <v>0.06069589703185985</v>
+        <v>0.1089223507903111</v>
       </c>
       <c r="AI12">
-        <v>0.09046732407614209</v>
+        <v>0.1224131734203696</v>
       </c>
       <c r="AJ12">
-        <v>-0.3422142796264737</v>
+        <v>-0.0803577454745866</v>
       </c>
       <c r="AK12">
-        <v>-0.6459850869506695</v>
+        <v>-0.09275085332478862</v>
       </c>
       <c r="AL12">
-        <v>0.095</v>
+        <v>0.066</v>
       </c>
       <c r="AM12">
-        <v>0.095</v>
+        <v>0.066</v>
       </c>
       <c r="AN12">
-        <v>3.623711340206185</v>
+        <v>-2.700534759358289</v>
       </c>
       <c r="AO12">
-        <v>-0.6105263157894737</v>
+        <v>-9.742424242424242</v>
       </c>
       <c r="AP12">
-        <v>-18.79362600432297</v>
+        <v>1.881393710926484</v>
       </c>
       <c r="AQ12">
-        <v>-0.6105263157894737</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Bangkok Insurance Public Company Limited (SET:BKI)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.108</v>
-      </c>
-      <c r="G13">
-        <v>0.06490021801106827</v>
-      </c>
-      <c r="H13">
-        <v>0.06490021801106827</v>
-      </c>
-      <c r="I13">
-        <v>-0.08385041086701325</v>
-      </c>
-      <c r="J13">
-        <v>-0.08385041086701325</v>
-      </c>
-      <c r="K13">
-        <v>-51.4</v>
-      </c>
-      <c r="L13">
-        <v>-0.08619822237128963</v>
-      </c>
-      <c r="M13">
-        <v>52.2</v>
-      </c>
-      <c r="N13">
-        <v>0.06074711974863262</v>
-      </c>
-      <c r="O13">
-        <v>-1.015564202334631</v>
-      </c>
-      <c r="P13">
-        <v>52.2</v>
-      </c>
-      <c r="Q13">
-        <v>0.06074711974863262</v>
-      </c>
-      <c r="R13">
-        <v>-1.015564202334631</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>20</v>
-      </c>
-      <c r="V13">
-        <v>0.02327475852438031</v>
-      </c>
-      <c r="W13">
-        <v>-0.05348595213319459</v>
-      </c>
-      <c r="X13">
-        <v>0.1001362285266533</v>
-      </c>
-      <c r="Y13">
-        <v>-0.1536221806598479</v>
-      </c>
-      <c r="Z13">
-        <v>0.6169684428349715</v>
-      </c>
-      <c r="AA13">
-        <v>-0.05173305742369374</v>
-      </c>
-      <c r="AB13">
-        <v>0.09895106375873021</v>
-      </c>
-      <c r="AC13">
-        <v>-0.1506841211824239</v>
-      </c>
-      <c r="AD13">
-        <v>22.4</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>22.4</v>
-      </c>
-      <c r="AG13">
-        <v>2.399999999999999</v>
-      </c>
-      <c r="AH13">
-        <v>0.02540546671203357</v>
-      </c>
-      <c r="AI13">
-        <v>0.0249832701316083</v>
-      </c>
-      <c r="AJ13">
-        <v>0.002785192062202621</v>
-      </c>
-      <c r="AK13">
-        <v>0.0027378507871321</v>
-      </c>
-      <c r="AL13">
-        <v>1.12</v>
-      </c>
-      <c r="AM13">
-        <v>1.12</v>
-      </c>
-      <c r="AN13">
-        <v>-0.4806866952789699</v>
-      </c>
-      <c r="AO13">
-        <v>-44.64285714285714</v>
-      </c>
-      <c r="AP13">
-        <v>-0.05150214592274675</v>
-      </c>
-      <c r="AQ13">
-        <v>-44.64285714285714</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Thailand</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Syn Mun Kong Insurance Public Company Limited (SET:SMK)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>-0.00228</v>
-      </c>
-      <c r="G14">
-        <v>-0.682552838789888</v>
-      </c>
-      <c r="H14">
-        <v>-0.682552838789888</v>
-      </c>
-      <c r="I14">
-        <v>-3.645144546973032</v>
-      </c>
-      <c r="J14">
-        <v>-3.645144546973032</v>
-      </c>
-      <c r="K14">
-        <v>-887.8</v>
-      </c>
-      <c r="L14">
-        <v>-3.679237463738085</v>
-      </c>
-      <c r="M14">
-        <v>-0</v>
-      </c>
-      <c r="N14">
-        <v>-0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>-0</v>
-      </c>
-      <c r="Q14">
-        <v>-0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>49.8</v>
-      </c>
-      <c r="V14">
-        <v>1.992</v>
-      </c>
-      <c r="W14">
-        <v>-9.88641425389755</v>
-      </c>
-      <c r="X14">
-        <v>0.1020881219066696</v>
-      </c>
-      <c r="Y14">
-        <v>-9.98850237580422</v>
-      </c>
-      <c r="AB14">
-        <v>0.09962518662751838</v>
-      </c>
-      <c r="AD14">
-        <v>1.36</v>
-      </c>
-      <c r="AE14">
-        <v>0.3068959229630742</v>
-      </c>
-      <c r="AF14">
-        <v>1.666895922963074</v>
-      </c>
-      <c r="AG14">
-        <v>-48.13310407703693</v>
-      </c>
-      <c r="AH14">
-        <v>0.06250805972238024</v>
-      </c>
-      <c r="AI14">
-        <v>-0.002073426152635884</v>
-      </c>
-      <c r="AJ14">
-        <v>2.080702352643468</v>
-      </c>
-      <c r="AK14">
-        <v>0.0563795685644323</v>
-      </c>
-      <c r="AL14">
-        <v>0.036</v>
-      </c>
-      <c r="AM14">
-        <v>0.036</v>
-      </c>
-      <c r="AN14">
-        <v>-0.001547719844499677</v>
-      </c>
-      <c r="AO14">
-        <v>-24436.11111111111</v>
-      </c>
-      <c r="AP14">
-        <v>0.05477688261573408</v>
-      </c>
-      <c r="AQ14">
-        <v>-24436.11111111111</v>
+        <v>-9.742424242424242</v>
       </c>
     </row>
   </sheetData>
